--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -492,22 +497,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6561.916</v>
+        <v>6561.874</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.000137</v>
+        <v>-0.000143</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.9259</v>
+        <v>-42.83</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1098</v>
+        <v>-65.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.696</v>
+        <v>0.1032</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0819</v>
+        <v>0.678</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0751</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +535,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6560.974</v>
+        <v>6561.847</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.00028</v>
+        <v>-0.000147</v>
       </c>
       <c r="F3" t="n">
-        <v>-83.96850000000001</v>
+        <v>-44.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07770000000000001</v>
+        <v>-67.97</v>
       </c>
       <c r="H3" t="n">
-        <v>4.044</v>
+        <v>0.1367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3686</v>
+        <v>0.947</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1734</v>
       </c>
     </row>
     <row r="4">
@@ -562,22 +573,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6562.003</v>
+        <v>6561.974</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.000123</v>
+        <v>-0.000128</v>
       </c>
       <c r="F4" t="n">
-        <v>-36.955</v>
+        <v>-38.27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.145</v>
+        <v>-64.27</v>
       </c>
       <c r="H4" t="n">
-        <v>0.759</v>
+        <v>0.1374</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1185</v>
+        <v>0.738</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1083</v>
       </c>
     </row>
     <row r="5">
@@ -597,22 +611,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6562.575</v>
+        <v>6561.932</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.6e-05</v>
+        <v>-0.000134</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.8187</v>
+        <v>-40.21</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1629</v>
+        <v>-66.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.911</v>
+        <v>0.1167</v>
       </c>
       <c r="I5" t="n">
-        <v>0.416</v>
+        <v>0.775</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1086</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +649,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6562.022</v>
+        <v>6561.971</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00012</v>
+        <v>-0.000128</v>
       </c>
       <c r="F6" t="n">
-        <v>-36.0982</v>
+        <v>-38.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0769</v>
+        <v>-65.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4.044</v>
+        <v>0.1378</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3732</v>
+        <v>0.895</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1697</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +687,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6562.418</v>
+        <v>6561.948</v>
       </c>
       <c r="E7" t="n">
-        <v>-6e-05</v>
+        <v>-0.000132</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.987</v>
+        <v>-39.49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1249</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.001</v>
+        <v>0.1122</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3583</v>
+        <v>0.878</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1357</v>
       </c>
     </row>
     <row r="8">
@@ -702,22 +725,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6561.916</v>
+        <v>6561.917</v>
       </c>
       <c r="E8" t="n">
         <v>-0.000136</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.9153</v>
+        <v>-40.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1121</v>
+        <v>-70.11</v>
       </c>
       <c r="H8" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.754</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.091</v>
+      <c r="J8" t="n">
+        <v>0.0912</v>
       </c>
     </row>
     <row r="9">
@@ -737,22 +763,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6562.159</v>
+        <v>6562.001</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.899999999999999e-05</v>
+        <v>-0.000124</v>
       </c>
       <c r="F9" t="n">
-        <v>-29.8086</v>
+        <v>-37.03</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1626</v>
+        <v>-66.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.106</v>
+        <v>0.1343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.271</v>
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1702</v>
       </c>
     </row>
     <row r="10">
@@ -772,22 +801,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6562.146</v>
+        <v>6561.975</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.000101</v>
+        <v>-0.000128</v>
       </c>
       <c r="F10" t="n">
-        <v>-30.4259</v>
+        <v>-38.23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1266</v>
+        <v>-67.59</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93</v>
+        <v>0.0979</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1785</v>
+        <v>0.841</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0886</v>
       </c>
     </row>
     <row r="11">
@@ -807,22 +839,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6562.143</v>
+        <v>6562.021</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.000102</v>
+        <v>-0.00012</v>
       </c>
       <c r="F11" t="n">
-        <v>-30.5629</v>
+        <v>-36.12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4792</v>
+        <v>-62.36</v>
       </c>
       <c r="H11" t="n">
-        <v>1.07</v>
+        <v>0.3388</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8097</v>
+        <v>0.961</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4558</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
@@ -499,8 +499,10 @@
       <c r="D2" t="n">
         <v>6561.874</v>
       </c>
-      <c r="E2" t="n">
-        <v>-0.000143</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>-42.83</v>
@@ -509,13 +511,13 @@
         <v>-65.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1032</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0751</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -537,8 +539,10 @@
       <c r="D3" t="n">
         <v>6561.847</v>
       </c>
-      <c r="E3" t="n">
-        <v>-0.000147</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-0.00015</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>-44.1</v>
@@ -547,13 +551,13 @@
         <v>-67.97</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1367</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.947</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1734</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4">
@@ -575,8 +579,10 @@
       <c r="D4" t="n">
         <v>6561.974</v>
       </c>
-      <c r="E4" t="n">
-        <v>-0.000128</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>-38.27</v>
@@ -585,13 +591,13 @@
         <v>-64.27</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1374</v>
+        <v>0.14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1083</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="5">
@@ -613,8 +619,10 @@
       <c r="D5" t="n">
         <v>6561.932</v>
       </c>
-      <c r="E5" t="n">
-        <v>-0.000134</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>-40.21</v>
@@ -623,13 +631,13 @@
         <v>-66.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1167</v>
+        <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.775</v>
+        <v>0.77</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1086</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6">
@@ -651,8 +659,10 @@
       <c r="D6" t="n">
         <v>6561.971</v>
       </c>
-      <c r="E6" t="n">
-        <v>-0.000128</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>-38.4</v>
@@ -661,13 +671,13 @@
         <v>-65.98</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1378</v>
+        <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1697</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="7">
@@ -689,8 +699,10 @@
       <c r="D7" t="n">
         <v>6561.948</v>
       </c>
-      <c r="E7" t="n">
-        <v>-0.000132</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>-39.49</v>
@@ -699,13 +711,13 @@
         <v>-67.68000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1122</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1357</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="8">
@@ -727,8 +739,10 @@
       <c r="D8" t="n">
         <v>6561.917</v>
       </c>
-      <c r="E8" t="n">
-        <v>-0.000136</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>-40.9</v>
@@ -737,13 +751,13 @@
         <v>-70.11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1122</v>
+        <v>0.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0912</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="9">
@@ -765,8 +779,10 @@
       <c r="D9" t="n">
         <v>6562.001</v>
       </c>
-      <c r="E9" t="n">
-        <v>-0.000124</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>-37.03</v>
@@ -775,13 +791,13 @@
         <v>-66.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1343</v>
+        <v>0.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1702</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -803,8 +819,10 @@
       <c r="D10" t="n">
         <v>6561.975</v>
       </c>
-      <c r="E10" t="n">
-        <v>-0.000128</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>-38.23</v>
@@ -813,13 +831,13 @@
         <v>-67.59</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0979</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.841</v>
+        <v>0.84</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0886</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="11">
@@ -841,8 +859,10 @@
       <c r="D11" t="n">
         <v>6562.021</v>
       </c>
-      <c r="E11" t="n">
-        <v>-0.00012</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>-36.12</v>
@@ -851,13 +871,13 @@
         <v>-62.36</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3388</v>
+        <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.961</v>
+        <v>0.96</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4558</v>
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2018 y 2019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,41 +843,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Septiembre 21-2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6561.865</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-43.24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-71.54000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Agosto 05-2019</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Hα</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>6562.021</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6562.02</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>-0.00012</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>-36.12</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-62.36</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="F12" t="n">
+        <v>-36.19</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-62.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Agosto 06-2019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hα</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6562.015</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>-36.39</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-62.82</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.34</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.46</v>
       </c>
     </row>
   </sheetData>
